--- a/academias/Humanidades - Estadisticos 20232.xlsx
+++ b/academias/Humanidades - Estadisticos 20232.xlsx
@@ -1083,25 +1083,25 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>53.8</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>46.2</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1118,25 +1118,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1188,25 +1188,25 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1220,25 +1220,25 @@
         <v>98</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F6">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1287,25 +1287,25 @@
         <v>14</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1322,25 +1322,25 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9" s="1">
+        <v>70</v>
+      </c>
+      <c r="H9" s="1">
         <v>30</v>
       </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>100</v>
-      </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1357,25 +1357,25 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J10">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1392,25 +1392,25 @@
         <v>24</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J11">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1427,25 +1427,25 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1462,25 +1462,25 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1497,25 +1497,25 @@
         <v>37</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>13.5</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>187</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="F15">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>87.7</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>12.3</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J15">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>299</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="F16">
-        <v>299</v>
+        <v>55</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>18.4</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J16">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1644,16 +1644,16 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>65.40000000000001</v>
+        <v>53.8</v>
       </c>
       <c r="H2" s="1">
-        <v>34.6</v>
+        <v>46.2</v>
       </c>
       <c r="I2" s="2">
         <v>6.1</v>
@@ -1679,19 +1679,19 @@
         <v>32</v>
       </c>
       <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3" s="1">
+        <v>75</v>
+      </c>
+      <c r="H3" s="1">
         <v>25</v>
       </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="H3" s="1">
-        <v>21.9</v>
-      </c>
       <c r="I3" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>20</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1749,16 +1749,16 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H5" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2">
         <v>7</v>
@@ -1781,16 +1781,16 @@
         <v>98</v>
       </c>
       <c r="E6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G6" s="1">
-        <v>76.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>23.5</v>
+        <v>28.6</v>
       </c>
       <c r="I6" s="2">
         <v>6.8</v>
@@ -1828,7 +1828,7 @@
         <v>28.6</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>28.6</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1883,19 +1883,19 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>76.7</v>
+        <v>70</v>
       </c>
       <c r="H9" s="1">
-        <v>23.3</v>
+        <v>30</v>
       </c>
       <c r="I9" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1953,19 +1953,19 @@
         <v>24</v>
       </c>
       <c r="E11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="H11" s="1">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1988,19 +1988,19 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2023,19 +2023,19 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>67.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>32.1</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         <v>13.5</v>
       </c>
       <c r="I14" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>187</v>
       </c>
       <c r="E15">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1">
-        <v>86.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="H15" s="1">
-        <v>13.4</v>
+        <v>12.3</v>
       </c>
       <c r="I15" s="2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2119,19 +2119,19 @@
         <v>299</v>
       </c>
       <c r="E16">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F16">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G16" s="1">
-        <v>82.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>17.4</v>
+        <v>18.4</v>
       </c>
       <c r="I16" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J16">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20232.xlsx
+++ b/academias/Humanidades - Estadisticos 20232.xlsx
@@ -691,22 +691,22 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7">
         <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H7" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -723,22 +723,22 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H8" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -863,19 +863,19 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="H12" s="1">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2">
         <v>8.5</v>
@@ -965,19 +965,19 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E15">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F15">
         <v>25</v>
       </c>
       <c r="G15" s="1">
-        <v>86.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="H15" s="1">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="I15" s="2">
         <v>7.8</v>
@@ -994,19 +994,19 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E16">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F16">
         <v>52</v>
       </c>
       <c r="G16" s="1">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="H16" s="1">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I16" s="2">
         <v>7.3</v>
@@ -1252,22 +1252,22 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7">
         <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H7" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I7" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1284,22 +1284,22 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H8" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1526,22 +1526,22 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E15">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F15">
         <v>23</v>
       </c>
       <c r="G15" s="1">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="H15" s="1">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="I15" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1555,19 +1555,19 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E16">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F16">
         <v>55</v>
       </c>
       <c r="G16" s="1">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="H16" s="1">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="I16" s="2">
         <v>7.7</v>
@@ -1644,19 +1644,19 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>53.8</v>
+        <v>88.5</v>
       </c>
       <c r="H2" s="1">
-        <v>46.2</v>
+        <v>11.5</v>
       </c>
       <c r="I2" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1691,7 +1691,7 @@
         <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1714,19 +1714,19 @@
         <v>15</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>80</v>
+        <v>93.3</v>
       </c>
       <c r="H4" s="1">
-        <v>20</v>
+        <v>6.7</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1749,19 +1749,19 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1781,19 +1781,19 @@
         <v>98</v>
       </c>
       <c r="E6">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
-        <v>71.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H6" s="1">
-        <v>28.6</v>
+        <v>12.2</v>
       </c>
       <c r="I6" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>71.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="H7" s="1">
-        <v>28.6</v>
+        <v>13.3</v>
       </c>
       <c r="I7" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1845,22 +1845,22 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>71.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="H8" s="1">
-        <v>28.6</v>
+        <v>13.3</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1883,19 +1883,19 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H9" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1953,19 +1953,19 @@
         <v>24</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H11" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I11" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1985,10 +1985,10 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2023,19 +2023,19 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>75</v>
+        <v>85.7</v>
       </c>
       <c r="H13" s="1">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="I13" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2058,19 +2058,19 @@
         <v>37</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>86.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="I14" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2087,22 +2087,22 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E15">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="F15">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>87.7</v>
+        <v>94.7</v>
       </c>
       <c r="H15" s="1">
-        <v>12.3</v>
+        <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2116,22 +2116,22 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E16">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="F16">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="G16" s="1">
-        <v>81.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>18.4</v>
+        <v>7.9</v>
       </c>
       <c r="I16" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J16">
         <v>0</v>
